--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>24/08 18:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10.50</t>
-        </is>
+      <c r="F2" t="n">
+        <v>10.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>110</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>30/08 23:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>22/08 19:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>23/08 15:45</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>24/08 15:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>60</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>65</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>65</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>31/08 14:45</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>24/08 23:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>55</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>24/08 14:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>55</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>31/08 01:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>24/08 12:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>60</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>23/08 14:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>50</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>24/08 18:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>60</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>22/08 01:50</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="F21" t="n">
+        <v>1.95</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>23/08 13:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F22" t="n">
+        <v>4.25</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>50</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>23/08 11:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45891.07223085975</v>
+        <v>45891.07223085648</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,246 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>55</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+6,25%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45891.07223085648</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | H 2 (−2.5) | Alexander </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alexander Zverev – Alejandro TabiloUS Open - Qualifications (H)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+17,9%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45891.13187616412</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Reilly Ope</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Reilly Opelka – Carlos AlcarazUS Open - Qualifications (H)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+6,25%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45891.07223085975</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+7,17%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45891.13187616412</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Qingdao Ha</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Qingdao Hainiu FC – Shanghai ShenhuaSuper League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>23/08 11:35</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+6,58%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45891.13187616412</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | La Corogne</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>La Corogne – Burgos CFLaLiga2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+6,05%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45891.13187616412</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Llaneros F</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Llaneros FC – AD PastoPrimera A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23/08 01:10</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+5,13%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45891.13187616412</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>60</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45891.13187616412</v>
+        <v>45891.13187616898</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>55</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45891.13187616412</v>
+        <v>45891.13187616898</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>23/08 11:35</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>50</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45891.13187616412</v>
+        <v>45891.13187616898</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>50</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45891.13187616412</v>
+        <v>45891.13187616898</v>
       </c>
     </row>
     <row r="31">
@@ -1760,10 +1752,8 @@
           <t>23/08 01:10</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>45</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1776,7 +1766,52 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45891.13187616412</v>
+        <v>45891.13187616898</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 2 (−2.5) | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Vit KoprivaUS Open - Qualifications (H)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45891.18417298347</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>150</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,97 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45891.18417298347</v>
+        <v>45891.18417298611</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Spezia – C</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Spezia – CarrareseSerie B</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>24/08 17:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45891.22340447258</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 3.5 - tir cadré2e équipe | Heidenheim</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Heidenheim – WolfsburgAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>23/08 13:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>40,7%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+7,89%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45891.22340447258</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>50</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45891.22340447258</v>
+        <v>45891.22340446759</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>23/08 13:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.65</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,277 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45891.22340447258</v>
+        <v>45891.22340446759</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 18.5 - tirs2e équipe | Real Ovied</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Real Oviedo – Real MadridEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 18.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>24/08 19:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+21,9%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45891.27292783406</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Eibar – Gr</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Eibar – GrenadeLaLiga2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>22/08 17:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+20,8%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45891.27292783406</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 26.5 - tirs | Go Ahead E</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles – Sparta RotterdamPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>23/08 14:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+16,8%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45891.27292783406</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Sportivo AmelianoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>23/08 19:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45891.27292783406</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 8.5 - tir cadré | Telstar – </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Telstar – VolendamPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>23/08 19:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+10,1%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45891.27292783406</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Remplaçant marque un but: Oui | Levante – </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Levante – FC BarceloneLaLiga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>23/08 19:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45891.27292783406</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>24/08 19:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.85</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45891.27292783406</v>
+        <v>45891.27292783565</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>22/08 17:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>55</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45891.27292783406</v>
+        <v>45891.27292783565</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>23/08 14:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45891.27292783406</v>
+        <v>45891.27292783565</v>
       </c>
     </row>
     <row r="38">
@@ -2059,10 +2053,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>45</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2075,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45891.27292783406</v>
+        <v>45891.27292783565</v>
       </c>
     </row>
     <row r="39">
@@ -2104,10 +2096,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45891.27292783406</v>
+        <v>45891.27292783565</v>
       </c>
     </row>
     <row r="40">
@@ -2149,10 +2139,8 @@
           <t>23/08 19:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2165,7 +2153,97 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45891.27292783406</v>
+        <v>45891.27292783565</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 7.5 - tir cadré | Telstar – </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Telstar – VolendamPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>23/08 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>33,0%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+8,85%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45891.30573873735</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | EC Bahia –</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>EC Bahia – SantosSérie A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>24/08 19:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45891.30573873735</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F41" t="n">
+        <v>3.3</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45891.30573873735</v>
+        <v>45891.30573873843</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>24/08 19:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>55</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,187 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45891.30573873735</v>
+        <v>45891.30573873843</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | Gazisehir </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Gazisehir Gaziantep FK – GenclerbirligiTurquie - Turquie Super Lig</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23/08 18:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>45,1%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+39,7%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45891.35349613162</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 26.5 - tirs | Bragantino</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bragantino – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>23/08 19:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>45,3%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+24,5%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45891.35349613162</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 10.5 - tir cadré | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Internacional RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 10.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>23/08 21:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>30,4%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+18,4%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45891.35349613162</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 16.5 - tirs1re équipe | Bayern Mun</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bayern Munich – RB LeipzigAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Moins que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22/08 18:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+15,8%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45891.35349613162</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F43" t="n">
+        <v>3.1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45891.35349613162</v>
+        <v>45891.35349613426</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.75</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45891.35349613162</v>
+        <v>45891.35349613426</v>
       </c>
     </row>
     <row r="45">
@@ -2358,10 +2354,8 @@
           <t>23/08 21:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F45" t="n">
+        <v>3.9</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2374,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45891.35349613162</v>
+        <v>45891.35349613426</v>
       </c>
     </row>
     <row r="46">
@@ -2403,10 +2397,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F46" t="n">
+        <v>3.3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2419,7 +2411,97 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45891.35349613162</v>
+        <v>45891.35349613426</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 2 (−2.5) | Alexei Pop</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin – Emil RuusuvuoriUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,00%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+19,9%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45891.3912509508</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Union Sant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Union Santa Fe – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>24/08 17:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+12,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45891.3912509508</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>60</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45891.3912509508</v>
+        <v>45891.39125094908</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>55</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,97 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45891.3912509508</v>
+        <v>45891.39125094908</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Tigre –</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CA Tigre – Independiente RivadaviaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>22/08 23:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+51,4%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45891.43264325093</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | San Martin</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Martin de San Juan – Gimnasia La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>23/08 23:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+32,4%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45891.43264325093</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>22/08 23:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>60</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45891.43264325093</v>
+        <v>45891.43264325232</v>
       </c>
     </row>
     <row r="50">
@@ -2571,23 +2569,111 @@
           <t>23/08 23:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>60</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+32,4%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45891.43264325232</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Fatih Kara</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fatih Karagümrük – GoztepeTurquie - Turquie Super Lig</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>22/08 18:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+15,2%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45891.47087872411</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cruzeiro –</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cruzeiro – Sao PauloSérie A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>31/08 00:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>+32,4%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>45891.43264325093</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+14,4%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45891.47087872411</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.75</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45891.47087872411</v>
+        <v>45891.47087872685</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>31/08 00:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>60</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,97 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45891.47087872411</v>
+        <v>45891.47087872685</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FC Volenda</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FC Volendam – Ajax AmsterdamEredivisie - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>30/08 14:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+15,3%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45891.529498686</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 14.5 - tirs1re équipe | Bragantino</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bragantino – FluminenseBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>23/08 19:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+15,1%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45891.529498686</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -2698,10 +2698,8 @@
           <t>30/08 14:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>50</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45891.529498686</v>
+        <v>45891.52949868055</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>23/08 19:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F54" t="n">
+        <v>2.7</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45891.529498686</v>
+        <v>45891.52949868055</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2758,6 +2758,96 @@
         <v>45891.52949868055</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Tokyo Verd</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy – Sanfrecce HiroshimaJ-League</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>23/08 10:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+12,3%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45891.59810759489</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atlético B</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga – Rionegro AguilasPrimera A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>25/08 01:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+12,0%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45891.59810759489</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>23/08 10:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>50</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45891.59810759489</v>
+        <v>45891.5981075926</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>25/08 01:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>50</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,52 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45891.59810759489</v>
+        <v>45891.5981075926</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | HNK Rijeka</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HNK Rijeka – VarazdinHNL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>24/08 19:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+32,0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45891.6403661022</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>24/08 19:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>60</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,52 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45891.6403661022</v>
+        <v>45891.64036609953</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gremio – C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gremio – Ceara SCSérie A</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>24/08 00:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+11,6%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45891.68525801196</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -2913,10 +2913,8 @@
           <t>24/08 00:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>50</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2929,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45891.68525801196</v>
+        <v>45891.68525800926</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2930,6 +2930,96 @@
         <v>45891.68525800926</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | 1(0:2) | Korona Kie</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Korona Kielce – Motor LublinPologne - D1 Pologne</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1(0:2)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>23/08 15:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20,6%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+17,7%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45891.77107878535</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Aris Thess</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Aris Thessalonique – VolosSuper League</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>23/08 17:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+14,4%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45891.77107878535</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>23/08 15:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
+      <c r="F59" t="n">
+        <v>5.7</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45891.77107878535</v>
+        <v>45891.77107878472</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>23/08 17:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>50</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,52 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45891.77107878535</v>
+        <v>45891.77107878472</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tir cadré | Columbus C</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Columbus Crew – New England RevolutionÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>23/08 23:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>53,9%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+10,6%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45891.80431802238</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -3042,10 +3042,8 @@
           <t>23/08 23:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.05</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45891.80431802238</v>
+        <v>45891.80431802083</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3059,6 +3059,96 @@
         <v>45891.80431802083</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Tigre –</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CA Tigre – Independiente RivadaviaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>22/08 23:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+12,0%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45891.93064210161</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Mirandes –</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Mirandes – HuescaLaLiga2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>23/08 15:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+10,9%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45891.93064210161</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-22.xlsx
+++ b/data/valuebets_database_2025-08-22.xlsx
@@ -3085,10 +3085,8 @@
           <t>22/08 23:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>65</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45891.93064210161</v>
+        <v>45891.93064210648</v>
       </c>
     </row>
     <row r="63">
@@ -3130,10 +3128,8 @@
           <t>23/08 15:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>50</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3146,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45891.93064210161</v>
+        <v>45891.93064210648</v>
       </c>
     </row>
   </sheetData>
